--- a/data/slapi.xlsx
+++ b/data/slapi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{497BD5F8-BD4E-4DB0-B6FA-B1A14E1A926F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C47D95-9DB0-4EF8-85DA-63942E9CC95C}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{497BD5F8-BD4E-4DB0-B6FA-B1A14E1A926F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9223F7A1-556A-41D2-B91D-5F2F3B68C587}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="41">
   <si>
     <t>Fecha</t>
   </si>
@@ -161,12 +161,6 @@
   </si>
   <si>
     <t>Ganacias/Pérdidas Promedio Diario</t>
-  </si>
-  <si>
-    <t>INV14</t>
-  </si>
-  <si>
-    <t>INV15</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="22" bestFit="1" customWidth="1"/>
@@ -2013,7 +2007,7 @@
         <v>45809</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>11</v>
@@ -2059,7 +2053,7 @@
         <v>45839</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>11</v>
@@ -2105,41 +2099,231 @@
         <v>45870</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" ref="D24" si="60">+D23+K23+E23-F24</f>
+        <f t="shared" ref="D24:D28" si="60">+D23+K23+E23-F24</f>
         <v>28704.777000000006</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3375</v>
+      </c>
+      <c r="G24" s="2">
+        <v>449.12</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="53"/>
-        <v>7127.53</v>
+        <v>7576.65</v>
       </c>
       <c r="I24" s="24">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>44.912000000000006</v>
       </c>
       <c r="J24" s="24">
         <f t="shared" si="55"/>
-        <v>712.75300000000004</v>
+        <v>757.66500000000008</v>
       </c>
       <c r="K24" s="24">
         <f t="shared" si="56"/>
-        <v>0</v>
+        <v>404.20799999999997</v>
       </c>
       <c r="L24" s="24">
         <f t="shared" si="57"/>
-        <v>6414.777</v>
+        <v>6818.9849999999997</v>
       </c>
       <c r="M24" s="24">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>13.473599999999999</v>
       </c>
       <c r="N24" s="30">
         <f t="shared" si="59"/>
+        <v>1.5646176244462722E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="21">
+        <v>45901</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="60"/>
+        <v>32483.985000000004</v>
+      </c>
+      <c r="G25" s="2">
+        <v>747.13</v>
+      </c>
+      <c r="H25" s="24">
+        <f t="shared" ref="H25:H28" si="61">+H24+G25</f>
+        <v>8323.7799999999988</v>
+      </c>
+      <c r="I25" s="24">
+        <f t="shared" ref="I25:I28" si="62">+G25*0.1</f>
+        <v>74.713000000000008</v>
+      </c>
+      <c r="J25" s="24">
+        <f t="shared" ref="J25:J28" si="63">+J24+I25</f>
+        <v>832.37800000000004</v>
+      </c>
+      <c r="K25" s="24">
+        <f t="shared" ref="K25:K28" si="64">+G25-I25</f>
+        <v>672.41700000000003</v>
+      </c>
+      <c r="L25" s="24">
+        <f t="shared" ref="L25:L28" si="65">+L24+K25</f>
+        <v>7491.402</v>
+      </c>
+      <c r="M25" s="24">
+        <f t="shared" ref="M25:M28" si="66">+K25/30</f>
+        <v>22.413900000000002</v>
+      </c>
+      <c r="N25" s="30">
+        <f t="shared" ref="N25:N28" si="67">+G25/D25</f>
+        <v>2.2999949051817375E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="21">
+        <v>45931</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="2">
+        <f t="shared" si="60"/>
+        <v>33156.402000000002</v>
+      </c>
+      <c r="G26" s="2">
+        <v>969.28</v>
+      </c>
+      <c r="H26" s="24">
+        <f t="shared" si="61"/>
+        <v>9293.06</v>
+      </c>
+      <c r="I26" s="24">
+        <f t="shared" si="62"/>
+        <v>96.927999999999997</v>
+      </c>
+      <c r="J26" s="24">
+        <f t="shared" si="63"/>
+        <v>929.30600000000004</v>
+      </c>
+      <c r="K26" s="24">
+        <f t="shared" si="64"/>
+        <v>872.35199999999998</v>
+      </c>
+      <c r="L26" s="24">
+        <f t="shared" si="65"/>
+        <v>8363.7540000000008</v>
+      </c>
+      <c r="M26" s="24">
+        <f t="shared" si="66"/>
+        <v>29.078399999999998</v>
+      </c>
+      <c r="N26" s="30">
+        <f t="shared" si="67"/>
+        <v>2.9233570035735481E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="21">
+        <v>45962</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="60"/>
+        <v>34028.754000000001</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3375</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1225.04</v>
+      </c>
+      <c r="H27" s="24">
+        <f t="shared" si="61"/>
+        <v>10518.099999999999</v>
+      </c>
+      <c r="I27" s="24">
+        <f t="shared" si="62"/>
+        <v>122.504</v>
+      </c>
+      <c r="J27" s="24">
+        <f t="shared" si="63"/>
+        <v>1051.81</v>
+      </c>
+      <c r="K27" s="24">
+        <f t="shared" si="64"/>
+        <v>1102.5360000000001</v>
+      </c>
+      <c r="L27" s="24">
+        <f t="shared" si="65"/>
+        <v>9466.2900000000009</v>
+      </c>
+      <c r="M27" s="24">
+        <f t="shared" si="66"/>
+        <v>36.751200000000004</v>
+      </c>
+      <c r="N27" s="30">
+        <f t="shared" si="67"/>
+        <v>3.6000142702844774E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="21">
+        <v>45992</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="2">
+        <f t="shared" si="60"/>
+        <v>38506.29</v>
+      </c>
+      <c r="H28" s="24">
+        <f t="shared" si="61"/>
+        <v>10518.099999999999</v>
+      </c>
+      <c r="I28" s="24">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="24">
+        <f t="shared" si="63"/>
+        <v>1051.81</v>
+      </c>
+      <c r="K28" s="24">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="24">
+        <f t="shared" si="65"/>
+        <v>9466.2900000000009</v>
+      </c>
+      <c r="M28" s="24">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="30">
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
     </row>

--- a/data/slapi.xlsx
+++ b/data/slapi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B9421F-4F4D-4E1D-A4EA-4FF6A0E45612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{32B9421F-4F4D-4E1D-A4EA-4FF6A0E45612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB914205-C570-4A22-A29B-C718B91B2E1D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{7A27F12D-6F9D-4758-B7D5-03B08667753E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="41">
   <si>
     <t>Fecha</t>
   </si>
@@ -1015,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EEB1E01-21BC-442C-965D-94DEC222FAE4}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" style="22" bestFit="1" customWidth="1"/>
@@ -2439,33 +2439,177 @@
         <f t="shared" si="68"/>
         <v>43837.106999999996</v>
       </c>
+      <c r="G31" s="2">
+        <v>559.95000000000005</v>
+      </c>
       <c r="H31" s="24">
         <f t="shared" si="69"/>
-        <v>12691.229999999998</v>
+        <v>13251.179999999998</v>
       </c>
       <c r="I31" s="24">
         <f t="shared" si="70"/>
-        <v>0</v>
+        <v>55.995000000000005</v>
       </c>
       <c r="J31" s="24">
         <f t="shared" si="71"/>
-        <v>1269.123</v>
+        <v>1325.1179999999999</v>
       </c>
       <c r="K31" s="24">
         <f t="shared" si="72"/>
-        <v>0</v>
+        <v>503.95500000000004</v>
       </c>
       <c r="L31" s="24">
         <f t="shared" si="73"/>
-        <v>11422.107000000002</v>
+        <v>11926.062000000002</v>
       </c>
       <c r="M31" s="24">
         <f t="shared" si="74"/>
-        <v>0</v>
+        <v>16.798500000000001</v>
       </c>
       <c r="N31" s="30">
         <f t="shared" si="75"/>
-        <v>0</v>
+        <v>1.2773425034640176E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="21">
+        <v>46113</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="2">
+        <f t="shared" ref="D32:D34" si="76">+D31+K31+E31-F32</f>
+        <v>44341.061999999998</v>
+      </c>
+      <c r="G32" s="2">
+        <v>298.88</v>
+      </c>
+      <c r="H32" s="24">
+        <f t="shared" ref="H32:H34" si="77">+H31+G32</f>
+        <v>13550.059999999998</v>
+      </c>
+      <c r="I32" s="24">
+        <f t="shared" ref="I32:I34" si="78">+G32*0.1</f>
+        <v>29.888000000000002</v>
+      </c>
+      <c r="J32" s="24">
+        <f t="shared" ref="J32:J34" si="79">+J31+I32</f>
+        <v>1355.0059999999999</v>
+      </c>
+      <c r="K32" s="24">
+        <f t="shared" ref="K32:K34" si="80">+G32-I32</f>
+        <v>268.99200000000002</v>
+      </c>
+      <c r="L32" s="24">
+        <f t="shared" ref="L32:L34" si="81">+L31+K32</f>
+        <v>12195.054000000002</v>
+      </c>
+      <c r="M32" s="24">
+        <f t="shared" ref="M32:M34" si="82">+K32/30</f>
+        <v>8.9664000000000001</v>
+      </c>
+      <c r="N32" s="30">
+        <f t="shared" ref="N32:N34" si="83">+G32/D32</f>
+        <v>6.7404790620486264E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="21">
+        <v>46143</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" si="76"/>
+        <v>44610.053999999996</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3375</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1060</v>
+      </c>
+      <c r="H33" s="24">
+        <f t="shared" si="77"/>
+        <v>14610.059999999998</v>
+      </c>
+      <c r="I33" s="24">
+        <f t="shared" si="78"/>
+        <v>106</v>
+      </c>
+      <c r="J33" s="24">
+        <f t="shared" si="79"/>
+        <v>1461.0059999999999</v>
+      </c>
+      <c r="K33" s="24">
+        <f t="shared" si="80"/>
+        <v>954</v>
+      </c>
+      <c r="L33" s="24">
+        <f t="shared" si="81"/>
+        <v>13149.054000000002</v>
+      </c>
+      <c r="M33" s="24">
+        <f t="shared" si="82"/>
+        <v>31.8</v>
+      </c>
+      <c r="N33" s="30">
+        <f t="shared" si="83"/>
+        <v>2.3761459692472016E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="21">
+        <v>46174</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2">
+        <f t="shared" si="76"/>
+        <v>48939.053999999996</v>
+      </c>
+      <c r="G34" s="2">
+        <v>892.12</v>
+      </c>
+      <c r="H34" s="24">
+        <f t="shared" si="77"/>
+        <v>15502.179999999998</v>
+      </c>
+      <c r="I34" s="24">
+        <f t="shared" si="78"/>
+        <v>89.212000000000003</v>
+      </c>
+      <c r="J34" s="24">
+        <f t="shared" si="79"/>
+        <v>1550.2179999999998</v>
+      </c>
+      <c r="K34" s="24">
+        <f t="shared" si="80"/>
+        <v>802.90800000000002</v>
+      </c>
+      <c r="L34" s="24">
+        <f t="shared" si="81"/>
+        <v>13951.962000000001</v>
+      </c>
+      <c r="M34" s="24">
+        <f t="shared" si="82"/>
+        <v>26.7636</v>
+      </c>
+      <c r="N34" s="30">
+        <f t="shared" si="83"/>
+        <v>1.8229204021802302E-2</v>
       </c>
     </row>
   </sheetData>
